--- a/clientes.xlsx
+++ b/clientes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="185">
   <si>
     <t>Nº</t>
   </si>
@@ -85,9 +85,6 @@
   </si>
   <si>
     <t>Ivan/Marcelo (Secretario)</t>
-  </si>
-  <si>
-    <t>444</t>
   </si>
   <si>
     <t>MARIA TELLO PELLITERO</t>
@@ -1051,205 +1048,203 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="E7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="H8" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>75</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>11</v>
@@ -1260,48 +1255,48 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="G12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>11</v>
@@ -1312,22 +1307,22 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>11</v>
@@ -1338,77 +1333,77 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="G15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="G16" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="H16" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>11</v>
@@ -1416,48 +1411,48 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="G18" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="H18" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>11</v>
@@ -1468,48 +1463,48 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C20" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="G20" s="2" t="s">
         <v>11</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C21" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>125</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>11</v>
@@ -1520,25 +1515,25 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="G22" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>131</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>11</v>
@@ -1546,25 +1541,25 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="C23" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="G23" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>136</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>11</v>
@@ -1572,25 +1567,25 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>11</v>
@@ -1598,25 +1593,25 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="C25" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="2" t="s">
+      <c r="G25" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>11</v>
@@ -1624,25 +1619,25 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="C26" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="2" t="s">
+      <c r="G26" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>11</v>
@@ -1650,77 +1645,77 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="C27" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="2" t="s">
+      <c r="G27" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="C28" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="2" t="s">
+      <c r="G28" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="H28" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="C29" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="2" t="s">
+      <c r="G29" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>161</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>11</v>
@@ -1728,25 +1723,25 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="C30" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" s="2" t="s">
+      <c r="G30" s="2" t="s">
         <v>164</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>165</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>11</v>
@@ -1754,25 +1749,25 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="C31" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="D31" s="2" t="s">
+      <c r="E31" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" s="2" t="s">
+      <c r="G31" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>170</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>11</v>
@@ -1780,25 +1775,25 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="C32" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="2" t="s">
+      <c r="G32" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>175</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>11</v>
@@ -1806,25 +1801,25 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="D33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" s="2" t="s">
+      <c r="G33" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>180</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>11</v>
@@ -1832,25 +1827,25 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="C34" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="D34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" s="2" t="s">
+      <c r="G34" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>185</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>11</v>
